--- a/Result/profitability/2362.xlsx
+++ b/Result/profitability/2362.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.45625</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>21.1675</v>
+        <v>20.905</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>0.50625</v>
+        <v>0.83375</v>
       </c>
       <c r="N3" t="n">
-        <v>20.76375</v>
+        <v>20.46</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.34</v>
       </c>
       <c r="M4" t="n">
-        <v>0.44625</v>
+        <v>0.8224999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>20.45375</v>
+        <v>19.08875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>0.46375</v>
+        <v>0.94375</v>
       </c>
       <c r="N5" t="n">
-        <v>19.92625</v>
+        <v>19.37</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,13 +1036,13 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>-0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4962499999999999</v>
+        <v>0.73375</v>
       </c>
       <c r="N6" t="n">
-        <v>19.76375</v>
+        <v>19.36375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3675</v>
+        <v>0.7375</v>
       </c>
       <c r="N7" t="n">
-        <v>19.8125</v>
+        <v>19.35875</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.85</v>
       </c>
       <c r="M8" t="n">
-        <v>0.41375</v>
+        <v>0.7675</v>
       </c>
       <c r="N8" t="n">
-        <v>19.675</v>
+        <v>19.21125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2362</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6530</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5408</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1121</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>342</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.24%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1837</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2179</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1989</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8787499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4.639344262295082</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.709999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1776819923371646</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.449999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2058279370952821</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
